--- a/Manual-Testing/Q2_TestCases.xlsx
+++ b/Manual-Testing/Q2_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\ecommerce-automation-test\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08B1546-63E7-4F37-B429-B7F6AC162279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFAB131-EF21-459A-AC19-AC59D2A595F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>TC_001</t>
-  </si>
-  <si>
-    <t>Login</t>
   </si>
   <si>
     <t>High</t>
@@ -163,6 +160,9 @@
 https://www.saucedemo.com/
 </t>
     </r>
+  </si>
+  <si>
+    <t>CartToCheckout</t>
   </si>
 </sst>
 </file>
@@ -554,7 +554,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="7" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -568,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>9</v>
@@ -600,34 +600,34 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="L3" s="1"/>
     </row>

--- a/Manual-Testing/Q2_TestCases.xlsx
+++ b/Manual-Testing/Q2_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\ecommerce-automation-test\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFAB131-EF21-459A-AC19-AC59D2A595F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD8F637-2929-493E-BAEE-749FE468EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
